--- a/docs/Plantilla_Pisos_Ubicaciones.xlsx
+++ b/docs/Plantilla_Pisos_Ubicaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAA0650-9D6C-44A4-B29B-A4D3D982B942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F242842-D84E-41D0-93E0-8FB7010F9376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,7 @@
     <sheet name="Ubicaciones" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Ubicaciones!$A$1:$H$356</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Ubicaciones!$A$1:$H$355</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="338">
   <si>
     <t>PLANTILLA DE PISOS Y UBICACIONES — Control de Visitantes (Clínica Santa Bárbara)</t>
   </si>
@@ -209,6 +209,33 @@
     <t>Sillón 12</t>
   </si>
   <si>
+    <t>Cubículo 10</t>
+  </si>
+  <si>
+    <t>Cubículo 11</t>
+  </si>
+  <si>
+    <t>Cubículo 12</t>
+  </si>
+  <si>
+    <t>Cubículo 13</t>
+  </si>
+  <si>
+    <t>Cubículo 14</t>
+  </si>
+  <si>
+    <t>Cubículo 15</t>
+  </si>
+  <si>
+    <t>Cubículo 16</t>
+  </si>
+  <si>
+    <t>Cubículo 17</t>
+  </si>
+  <si>
+    <t>Cubículo 18</t>
+  </si>
+  <si>
     <t>Sillón 13</t>
   </si>
   <si>
@@ -452,63 +479,9 @@
     <t>Piso 2 Hospitalización</t>
   </si>
   <si>
-    <t>CI 01</t>
-  </si>
-  <si>
     <t>CUIDADO INTENSIVO 5 PISO</t>
   </si>
   <si>
-    <t>CI 02</t>
-  </si>
-  <si>
-    <t>CI 03</t>
-  </si>
-  <si>
-    <t>CI 04</t>
-  </si>
-  <si>
-    <t>CI 05</t>
-  </si>
-  <si>
-    <t>CI 06</t>
-  </si>
-  <si>
-    <t>CI 07</t>
-  </si>
-  <si>
-    <t>CI 08</t>
-  </si>
-  <si>
-    <t>CI 09</t>
-  </si>
-  <si>
-    <t>CI 10</t>
-  </si>
-  <si>
-    <t>CI 11</t>
-  </si>
-  <si>
-    <t>CI 12</t>
-  </si>
-  <si>
-    <t>CI 13</t>
-  </si>
-  <si>
-    <t>CI 14</t>
-  </si>
-  <si>
-    <t>CI 15</t>
-  </si>
-  <si>
-    <t>CI 16</t>
-  </si>
-  <si>
-    <t>CI 17</t>
-  </si>
-  <si>
-    <t>CI 18</t>
-  </si>
-  <si>
     <t>HOSPITALIZACION 7 PISO</t>
   </si>
   <si>
@@ -701,18 +674,6 @@
     <t>Camilla 24</t>
   </si>
   <si>
-    <t>Sillon 25</t>
-  </si>
-  <si>
-    <t>Sillon 26</t>
-  </si>
-  <si>
-    <t>Sillon 27</t>
-  </si>
-  <si>
-    <t>Sillon 28</t>
-  </si>
-  <si>
     <t>Esclusa 1</t>
   </si>
   <si>
@@ -722,21 +683,9 @@
     <t>Pediatria</t>
   </si>
   <si>
-    <t>Sillon  1</t>
-  </si>
-  <si>
     <t>URGENCIAS PEDIATRÍA URG</t>
   </si>
   <si>
-    <t>Sillon 2</t>
-  </si>
-  <si>
-    <t>Sillon 3</t>
-  </si>
-  <si>
-    <t>Sillon 6</t>
-  </si>
-  <si>
     <t>Cuna 11</t>
   </si>
   <si>
@@ -764,21 +713,6 @@
     <t>Camilla 37</t>
   </si>
   <si>
-    <t>Sillon 38</t>
-  </si>
-  <si>
-    <t>Sillon 39</t>
-  </si>
-  <si>
-    <t>Sillon 40</t>
-  </si>
-  <si>
-    <t>Sillon 41</t>
-  </si>
-  <si>
-    <t>Sillon 42</t>
-  </si>
-  <si>
     <t>Camilla 43</t>
   </si>
   <si>
@@ -797,60 +731,12 @@
     <t>Camilla 48</t>
   </si>
   <si>
-    <t>Sillon 49</t>
-  </si>
-  <si>
-    <t>Sillon 50</t>
-  </si>
-  <si>
-    <t>Sillon 51</t>
-  </si>
-  <si>
-    <t>Sillon 52</t>
-  </si>
-  <si>
-    <t>Sillon 53</t>
-  </si>
-  <si>
-    <t>Sillon 54</t>
-  </si>
-  <si>
-    <t>Sillon 55</t>
-  </si>
-  <si>
-    <t>Sillon 56</t>
-  </si>
-  <si>
     <t>Zona D</t>
   </si>
   <si>
     <t>Camilla 59</t>
   </si>
   <si>
-    <t>Sillon 60</t>
-  </si>
-  <si>
-    <t>Sillon 61</t>
-  </si>
-  <si>
-    <t>Sillon 62</t>
-  </si>
-  <si>
-    <t>Sillon 63</t>
-  </si>
-  <si>
-    <t>Sillon 64</t>
-  </si>
-  <si>
-    <t>Sillon 65</t>
-  </si>
-  <si>
-    <t>Sillon 66</t>
-  </si>
-  <si>
-    <t>Sillon 67</t>
-  </si>
-  <si>
     <t>Camilla 68</t>
   </si>
   <si>
@@ -860,39 +746,6 @@
     <t>Camilla 70</t>
   </si>
   <si>
-    <t>Sillon 71</t>
-  </si>
-  <si>
-    <t>Sillon 72</t>
-  </si>
-  <si>
-    <t>Sillon 73</t>
-  </si>
-  <si>
-    <t>Sillon 74</t>
-  </si>
-  <si>
-    <t>Sillon 75</t>
-  </si>
-  <si>
-    <t>Sillon 76</t>
-  </si>
-  <si>
-    <t>Sillon 77</t>
-  </si>
-  <si>
-    <t>Silla  78</t>
-  </si>
-  <si>
-    <t>Silla  79</t>
-  </si>
-  <si>
-    <t>Silla  80</t>
-  </si>
-  <si>
-    <t>Silla  81</t>
-  </si>
-  <si>
     <t>Zona E</t>
   </si>
   <si>
@@ -995,21 +848,6 @@
     <t>Sala Proc. Camilla 2</t>
   </si>
   <si>
-    <t>Sillon 29</t>
-  </si>
-  <si>
-    <t>Sillon 30</t>
-  </si>
-  <si>
-    <t>Sillon 31</t>
-  </si>
-  <si>
-    <t>Sillon 32</t>
-  </si>
-  <si>
-    <t>Sillon 57</t>
-  </si>
-  <si>
     <t>Camilla 82</t>
   </si>
   <si>
@@ -1025,151 +863,190 @@
     <t>Reanimacion 5</t>
   </si>
   <si>
-    <t>Sillon 85</t>
-  </si>
-  <si>
-    <t>Sillon 86</t>
-  </si>
-  <si>
-    <t>Sillon 87</t>
-  </si>
-  <si>
-    <t>Sillon 88</t>
-  </si>
-  <si>
-    <t>Sillon 89</t>
-  </si>
-  <si>
-    <t>Sillon 90</t>
-  </si>
-  <si>
-    <t>Sillon 91</t>
-  </si>
-  <si>
-    <t>Sillon 92</t>
-  </si>
-  <si>
-    <t>Sillon 93</t>
-  </si>
-  <si>
-    <t>Sillon 94</t>
-  </si>
-  <si>
-    <t>Sillon 95</t>
-  </si>
-  <si>
-    <t>Sillon 96</t>
-  </si>
-  <si>
-    <t>Sillon 97</t>
-  </si>
-  <si>
-    <t>Sillon 98</t>
-  </si>
-  <si>
-    <t>Sillon 99</t>
-  </si>
-  <si>
-    <t>Sillon 100</t>
-  </si>
-  <si>
-    <t>Sillon 101</t>
-  </si>
-  <si>
-    <t>Sillon 102</t>
-  </si>
-  <si>
-    <t>Sillon 103</t>
-  </si>
-  <si>
-    <t>Sillon 104</t>
-  </si>
-  <si>
-    <t>Sillon 105</t>
-  </si>
-  <si>
-    <t>SILL01</t>
-  </si>
-  <si>
-    <t>SILL02</t>
-  </si>
-  <si>
-    <t>SILL03</t>
-  </si>
-  <si>
-    <t>SILL04</t>
-  </si>
-  <si>
-    <t>SILL05</t>
-  </si>
-  <si>
-    <t>SILL06</t>
-  </si>
-  <si>
-    <t>SILL07</t>
-  </si>
-  <si>
-    <t>SILL08</t>
-  </si>
-  <si>
-    <t>SILL09</t>
-  </si>
-  <si>
-    <t>SILL10</t>
-  </si>
-  <si>
-    <t>SILL11</t>
-  </si>
-  <si>
-    <t>SILL12</t>
-  </si>
-  <si>
-    <t>CAMI01</t>
-  </si>
-  <si>
-    <t>CE 01</t>
-  </si>
-  <si>
     <t>CUIDADOS INTERMEDIOS</t>
   </si>
   <si>
-    <t>CE 02</t>
-  </si>
-  <si>
-    <t>CE 03</t>
-  </si>
-  <si>
-    <t>CE 04</t>
-  </si>
-  <si>
-    <t>CE 05</t>
-  </si>
-  <si>
-    <t>CE 06</t>
-  </si>
-  <si>
-    <t>CE 07</t>
-  </si>
-  <si>
-    <t>CE 08</t>
-  </si>
-  <si>
-    <t>CE 09</t>
-  </si>
-  <si>
-    <t>CE 10</t>
-  </si>
-  <si>
-    <t>CE 11</t>
-  </si>
-  <si>
-    <t>CE 12</t>
-  </si>
-  <si>
-    <t>CE 13</t>
-  </si>
-  <si>
-    <t>CE 14</t>
+    <t>Cubículo 01</t>
+  </si>
+  <si>
+    <t>Cubículo 02</t>
+  </si>
+  <si>
+    <t>Cubículo 03</t>
+  </si>
+  <si>
+    <t>Cubículo 04</t>
+  </si>
+  <si>
+    <t>Cubículo 05</t>
+  </si>
+  <si>
+    <t>Cubículo 06</t>
+  </si>
+  <si>
+    <t>Cubículo 07</t>
+  </si>
+  <si>
+    <t>Cubículo 08</t>
+  </si>
+  <si>
+    <t>Cubículo 09</t>
+  </si>
+  <si>
+    <t>Sillón 49</t>
+  </si>
+  <si>
+    <t>Sillón 50</t>
+  </si>
+  <si>
+    <t>Sillón 51</t>
+  </si>
+  <si>
+    <t>Sillón 52</t>
+  </si>
+  <si>
+    <t>Sillón 53</t>
+  </si>
+  <si>
+    <t>Sillón 54</t>
+  </si>
+  <si>
+    <t>Sillón 55</t>
+  </si>
+  <si>
+    <t>Sillón 56</t>
+  </si>
+  <si>
+    <t>Sillón 60</t>
+  </si>
+  <si>
+    <t>Sillón 61</t>
+  </si>
+  <si>
+    <t>Sillón 62</t>
+  </si>
+  <si>
+    <t>Sillón 63</t>
+  </si>
+  <si>
+    <t>Sillón 64</t>
+  </si>
+  <si>
+    <t>Sillón 65</t>
+  </si>
+  <si>
+    <t>Sillón 66</t>
+  </si>
+  <si>
+    <t>Sillón 67</t>
+  </si>
+  <si>
+    <t>Sillón 71</t>
+  </si>
+  <si>
+    <t>Sillón 72</t>
+  </si>
+  <si>
+    <t>Sillón 73</t>
+  </si>
+  <si>
+    <t>Sillón 74</t>
+  </si>
+  <si>
+    <t>Sillón 75</t>
+  </si>
+  <si>
+    <t>Sillón 76</t>
+  </si>
+  <si>
+    <t>Sillón 77</t>
+  </si>
+  <si>
+    <t>Sillón  78</t>
+  </si>
+  <si>
+    <t>Sillón 79</t>
+  </si>
+  <si>
+    <t>Sillón  80</t>
+  </si>
+  <si>
+    <t>Sillón  81</t>
+  </si>
+  <si>
+    <t>Sillón 57</t>
+  </si>
+  <si>
+    <t>Sillón 85</t>
+  </si>
+  <si>
+    <t>Sillón 25</t>
+  </si>
+  <si>
+    <t>Sillón 26</t>
+  </si>
+  <si>
+    <t>Sillón 27</t>
+  </si>
+  <si>
+    <t>Sillón 86</t>
+  </si>
+  <si>
+    <t>Sillón 87</t>
+  </si>
+  <si>
+    <t>Sillón 88</t>
+  </si>
+  <si>
+    <t>Sillón 89</t>
+  </si>
+  <si>
+    <t>Sillón 90</t>
+  </si>
+  <si>
+    <t>Sillón 91</t>
+  </si>
+  <si>
+    <t>Sillón 92</t>
+  </si>
+  <si>
+    <t>Sillón 93</t>
+  </si>
+  <si>
+    <t>Sillón 94</t>
+  </si>
+  <si>
+    <t>Sillón 95</t>
+  </si>
+  <si>
+    <t>Sillón 96</t>
+  </si>
+  <si>
+    <t>Sillón 97</t>
+  </si>
+  <si>
+    <t>Sillón 98</t>
+  </si>
+  <si>
+    <t>Sillón 99</t>
+  </si>
+  <si>
+    <t>Sillón 100</t>
+  </si>
+  <si>
+    <t>Sillón 101</t>
+  </si>
+  <si>
+    <t>Sillón 102</t>
+  </si>
+  <si>
+    <t>Sillón 103</t>
+  </si>
+  <si>
+    <t>Sillón 104</t>
+  </si>
+  <si>
+    <t>Sillón 105</t>
   </si>
 </sst>
 </file>
@@ -1745,7 +1622,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1762,7 +1639,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1776,10 +1653,10 @@
         <v>22</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1796,7 +1673,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1859,7 +1736,7 @@
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E11:E108 E2:E9" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="E11:E108 E2:E3 E4:E9" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1870,7 +1747,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H356"/>
+  <dimension ref="A1:H355"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="5" customWidth="1"/>
@@ -1913,14 +1790,14 @@
         <v>22</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7" t="s">
         <v>46</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F2" s="5">
         <v>1</v>
@@ -1937,14 +1814,14 @@
         <v>22</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7" t="s">
         <v>47</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F3" s="5">
         <v>1</v>
@@ -1961,14 +1838,14 @@
         <v>22</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
         <v>48</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F4" s="5">
         <v>1</v>
@@ -1985,14 +1862,14 @@
         <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7" t="s">
         <v>49</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F5" s="5">
         <v>1</v>
@@ -2009,14 +1886,14 @@
         <v>22</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7" t="s">
         <v>50</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F6" s="5">
         <v>1</v>
@@ -2033,14 +1910,14 @@
         <v>22</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7" t="s">
         <v>51</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F7" s="5">
         <v>1</v>
@@ -2057,14 +1934,14 @@
         <v>22</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7" t="s">
         <v>52</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -2081,14 +1958,14 @@
         <v>22</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
         <v>53</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F9" s="5">
         <v>1</v>
@@ -2105,14 +1982,14 @@
         <v>22</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7" t="s">
         <v>54</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F10" s="5">
         <v>1</v>
@@ -2129,14 +2006,14 @@
         <v>22</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F11" s="5">
         <v>1</v>
@@ -2153,14 +2030,14 @@
         <v>22</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="s">
         <v>56</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F12" s="5">
         <v>1</v>
@@ -2177,14 +2054,14 @@
         <v>22</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7" t="s">
         <v>57</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F13" s="5">
         <v>1</v>
@@ -2201,14 +2078,14 @@
         <v>22</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F14" s="5">
         <v>1</v>
@@ -2225,14 +2102,14 @@
         <v>22</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F15" s="5">
         <v>1</v>
@@ -2249,14 +2126,14 @@
         <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F16" s="5">
         <v>1</v>
@@ -2273,14 +2150,14 @@
         <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -2297,14 +2174,14 @@
         <v>22</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F18" s="5">
         <v>1</v>
@@ -2321,14 +2198,14 @@
         <v>22</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F19" s="5">
         <v>1</v>
@@ -2345,14 +2222,14 @@
         <v>22</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F20" s="5">
         <v>1</v>
@@ -2369,14 +2246,14 @@
         <v>22</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F21" s="5">
         <v>1</v>
@@ -2393,14 +2270,14 @@
         <v>22</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F22" s="5">
         <v>1</v>
@@ -2417,14 +2294,14 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F23" s="5">
         <v>1</v>
@@ -2441,14 +2318,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F24" s="5">
         <v>1</v>
@@ -2465,14 +2342,14 @@
         <v>22</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F25" s="5">
         <v>1</v>
@@ -2489,14 +2366,14 @@
         <v>22</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7" t="s">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F26" s="5">
         <v>1</v>
@@ -2513,14 +2390,14 @@
         <v>22</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7" t="s">
-        <v>293</v>
+        <v>244</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F27" s="5">
         <v>1</v>
@@ -2537,14 +2414,14 @@
         <v>22</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7" t="s">
-        <v>294</v>
+        <v>245</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F28" s="5">
         <v>1</v>
@@ -2561,14 +2438,14 @@
         <v>22</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F29" s="5">
         <v>1</v>
@@ -2585,14 +2462,14 @@
         <v>22</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F30" s="5">
         <v>1</v>
@@ -2609,14 +2486,14 @@
         <v>22</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7" t="s">
-        <v>297</v>
+        <v>248</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F31" s="5">
         <v>1</v>
@@ -2633,14 +2510,14 @@
         <v>22</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7" t="s">
-        <v>298</v>
+        <v>249</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F32" s="5">
         <v>1</v>
@@ -2657,14 +2534,14 @@
         <v>22</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7" t="s">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F33" s="5">
         <v>1</v>
@@ -2681,14 +2558,14 @@
         <v>22</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7" t="s">
-        <v>300</v>
+        <v>251</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F34" s="5">
         <v>1</v>
@@ -2705,14 +2582,14 @@
         <v>22</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F35" s="5">
         <v>1</v>
@@ -2729,14 +2606,14 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F36" s="5">
         <v>1</v>
@@ -2753,14 +2630,14 @@
         <v>22</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F37" s="5">
         <v>1</v>
@@ -2777,14 +2654,14 @@
         <v>22</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F38" s="5">
         <v>1</v>
@@ -2801,14 +2678,14 @@
         <v>22</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7" t="s">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F39" s="5">
         <v>1</v>
@@ -2825,14 +2702,14 @@
         <v>22</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7" t="s">
-        <v>306</v>
+        <v>257</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F40" s="5">
         <v>1</v>
@@ -2849,14 +2726,14 @@
         <v>22</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7" t="s">
-        <v>307</v>
+        <v>258</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F41" s="5">
         <v>1</v>
@@ -2873,14 +2750,14 @@
         <v>22</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7" t="s">
-        <v>308</v>
+        <v>259</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F42" s="5">
         <v>1</v>
@@ -2897,14 +2774,14 @@
         <v>22</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7" t="s">
-        <v>309</v>
+        <v>260</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F43" s="5">
         <v>1</v>
@@ -2921,14 +2798,14 @@
         <v>22</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7" t="s">
-        <v>310</v>
+        <v>261</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F44" s="5">
         <v>1</v>
@@ -2945,14 +2822,14 @@
         <v>22</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7" t="s">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F45" s="5">
         <v>1</v>
@@ -2969,14 +2846,14 @@
         <v>22</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7" t="s">
-        <v>312</v>
+        <v>263</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F46" s="5">
         <v>1</v>
@@ -2993,14 +2870,14 @@
         <v>22</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7" t="s">
-        <v>313</v>
+        <v>264</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F47" s="5">
         <v>1</v>
@@ -3017,14 +2894,14 @@
         <v>22</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7" t="s">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F48" s="5">
         <v>1</v>
@@ -3041,14 +2918,14 @@
         <v>22</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F49" s="5">
         <v>1</v>
@@ -3065,14 +2942,14 @@
         <v>22</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F50" s="5">
         <v>1</v>
@@ -3089,14 +2966,14 @@
         <v>22</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F51" s="5">
         <v>1</v>
@@ -3113,14 +2990,14 @@
         <v>22</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F52" s="5">
         <v>1</v>
@@ -3137,14 +3014,14 @@
         <v>22</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7" t="s">
-        <v>319</v>
+        <v>270</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="F53" s="5">
         <v>1</v>
@@ -3161,14 +3038,14 @@
         <v>22</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7" t="s">
-        <v>139</v>
+        <v>277</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F54" s="5">
         <v>1</v>
@@ -3185,14 +3062,14 @@
         <v>22</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7" t="s">
-        <v>141</v>
+        <v>278</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F55" s="5">
         <v>1</v>
@@ -3209,14 +3086,14 @@
         <v>22</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7" t="s">
-        <v>142</v>
+        <v>279</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F56" s="5">
         <v>1</v>
@@ -3233,14 +3110,14 @@
         <v>22</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7" t="s">
-        <v>143</v>
+        <v>280</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F57" s="5">
         <v>1</v>
@@ -3257,14 +3134,14 @@
         <v>22</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7" t="s">
-        <v>144</v>
+        <v>281</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F58" s="5">
         <v>1</v>
@@ -3281,14 +3158,14 @@
         <v>22</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7" t="s">
-        <v>145</v>
+        <v>282</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F59" s="5">
         <v>1</v>
@@ -3305,14 +3182,14 @@
         <v>22</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7" t="s">
-        <v>146</v>
+        <v>283</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F60" s="5">
         <v>1</v>
@@ -3329,14 +3206,14 @@
         <v>22</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7" t="s">
-        <v>147</v>
+        <v>284</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F61" s="5">
         <v>1</v>
@@ -3353,14 +3230,14 @@
         <v>22</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="E62" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>140</v>
       </c>
       <c r="F62" s="5">
         <v>1</v>
@@ -3377,14 +3254,14 @@
         <v>22</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7" t="s">
-        <v>149</v>
+        <v>58</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F63" s="5">
         <v>1</v>
@@ -3401,14 +3278,14 @@
         <v>22</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7" t="s">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F64" s="5">
         <v>1</v>
@@ -3425,14 +3302,14 @@
         <v>22</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F65" s="5">
         <v>1</v>
@@ -3449,14 +3326,14 @@
         <v>22</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7" t="s">
-        <v>152</v>
+        <v>61</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F66" s="5">
         <v>1</v>
@@ -3473,14 +3350,14 @@
         <v>22</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F67" s="5">
         <v>1</v>
@@ -3497,14 +3374,14 @@
         <v>22</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7" t="s">
-        <v>154</v>
+        <v>63</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F68" s="5">
         <v>1</v>
@@ -3521,14 +3398,14 @@
         <v>22</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7" t="s">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F69" s="5">
         <v>1</v>
@@ -3545,14 +3422,14 @@
         <v>22</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="7" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F70" s="5">
         <v>1</v>
@@ -3569,14 +3446,14 @@
         <v>22</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="7" t="s">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F71" s="5">
         <v>1</v>
@@ -3593,16 +3470,14 @@
         <v>22</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>364</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C72" s="7"/>
       <c r="D72" s="7" t="s">
-        <v>364</v>
+        <v>277</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F72" s="5">
         <v>1</v>
@@ -3619,16 +3494,14 @@
         <v>22</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>366</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C73" s="7"/>
       <c r="D73" s="7" t="s">
-        <v>364</v>
+        <v>278</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F73" s="5">
         <v>1</v>
@@ -3645,16 +3518,14 @@
         <v>22</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>367</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C74" s="7"/>
       <c r="D74" s="7" t="s">
-        <v>366</v>
+        <v>279</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F74" s="5">
         <v>1</v>
@@ -3671,16 +3542,14 @@
         <v>22</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>368</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C75" s="7"/>
       <c r="D75" s="7" t="s">
-        <v>367</v>
+        <v>280</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F75" s="5">
         <v>1</v>
@@ -3697,16 +3566,14 @@
         <v>22</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>369</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C76" s="7"/>
       <c r="D76" s="7" t="s">
-        <v>368</v>
+        <v>281</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F76" s="5">
         <v>1</v>
@@ -3723,16 +3590,14 @@
         <v>22</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>370</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C77" s="7"/>
       <c r="D77" s="7" t="s">
-        <v>369</v>
+        <v>282</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F77" s="5">
         <v>1</v>
@@ -3749,16 +3614,14 @@
         <v>22</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>371</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C78" s="7"/>
       <c r="D78" s="7" t="s">
-        <v>370</v>
+        <v>283</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F78" s="5">
         <v>1</v>
@@ -3775,16 +3638,14 @@
         <v>22</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>372</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C79" s="7"/>
       <c r="D79" s="7" t="s">
-        <v>371</v>
+        <v>284</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F79" s="5">
         <v>1</v>
@@ -3801,16 +3662,14 @@
         <v>22</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>373</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C80" s="7"/>
       <c r="D80" s="7" t="s">
-        <v>372</v>
+        <v>285</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F80" s="5">
         <v>1</v>
@@ -3827,16 +3686,14 @@
         <v>22</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>374</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C81" s="7"/>
       <c r="D81" s="7" t="s">
-        <v>373</v>
+        <v>58</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F81" s="5">
         <v>1</v>
@@ -3853,16 +3710,14 @@
         <v>22</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>375</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C82" s="7"/>
       <c r="D82" s="7" t="s">
-        <v>374</v>
+        <v>59</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F82" s="5">
         <v>1</v>
@@ -3879,16 +3734,14 @@
         <v>22</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>376</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C83" s="7"/>
       <c r="D83" s="7" t="s">
-        <v>375</v>
+        <v>60</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F83" s="5">
         <v>1</v>
@@ -3905,16 +3758,14 @@
         <v>22</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>377</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C84" s="7"/>
       <c r="D84" s="7" t="s">
-        <v>376</v>
+        <v>61</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F84" s="5">
         <v>1</v>
@@ -3931,16 +3782,14 @@
         <v>22</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>378</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C85" s="7"/>
       <c r="D85" s="7" t="s">
-        <v>377</v>
+        <v>62</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="F85" s="5">
         <v>1</v>
@@ -3957,14 +3806,14 @@
         <v>22</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C86" s="7"/>
       <c r="D86" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F86" s="5">
         <v>1</v>
@@ -3981,14 +3830,14 @@
         <v>22</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C87" s="7"/>
       <c r="D87" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F87" s="5">
         <v>1</v>
@@ -4005,14 +3854,14 @@
         <v>22</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C88" s="7"/>
       <c r="D88" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F88" s="5">
         <v>1</v>
@@ -4029,14 +3878,14 @@
         <v>22</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C89" s="7"/>
       <c r="D89" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F89" s="5">
         <v>1</v>
@@ -4053,14 +3902,14 @@
         <v>22</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C90" s="7"/>
       <c r="D90" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F90" s="5">
         <v>1</v>
@@ -4077,14 +3926,14 @@
         <v>22</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7" t="s">
         <v>39</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F91" s="5">
         <v>1</v>
@@ -4101,14 +3950,14 @@
         <v>22</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F92" s="5">
         <v>1</v>
@@ -4125,14 +3974,14 @@
         <v>22</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7" t="s">
         <v>41</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F93" s="5">
         <v>1</v>
@@ -4149,14 +3998,14 @@
         <v>22</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7" t="s">
         <v>42</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F94" s="5">
         <v>1</v>
@@ -4173,14 +4022,14 @@
         <v>22</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7" t="s">
         <v>43</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F95" s="5">
         <v>1</v>
@@ -4197,14 +4046,14 @@
         <v>22</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="7" t="s">
         <v>44</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F96" s="5">
         <v>1</v>
@@ -4221,14 +4070,14 @@
         <v>22</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="7" t="s">
         <v>45</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F97" s="5">
         <v>1</v>
@@ -4245,14 +4094,14 @@
         <v>22</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C98" s="7"/>
       <c r="D98" s="7" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="F98" s="5">
         <v>1</v>
@@ -4273,10 +4122,10 @@
       </c>
       <c r="C99" s="7"/>
       <c r="D99" s="7" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F99" s="6">
         <v>2</v>
@@ -4297,10 +4146,10 @@
       </c>
       <c r="C100" s="7"/>
       <c r="D100" s="7" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F100" s="6">
         <v>2</v>
@@ -4321,10 +4170,10 @@
       </c>
       <c r="C101" s="7"/>
       <c r="D101" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F101" s="6">
         <v>2</v>
@@ -4345,10 +4194,10 @@
       </c>
       <c r="C102" s="7"/>
       <c r="D102" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F102" s="6">
         <v>2</v>
@@ -4369,10 +4218,10 @@
       </c>
       <c r="C103" s="7"/>
       <c r="D103" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F103" s="6">
         <v>2</v>
@@ -4393,10 +4242,10 @@
       </c>
       <c r="C104" s="7"/>
       <c r="D104" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F104" s="6">
         <v>2</v>
@@ -4417,10 +4266,10 @@
       </c>
       <c r="C105" s="7"/>
       <c r="D105" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F105" s="6">
         <v>2</v>
@@ -4441,10 +4290,10 @@
       </c>
       <c r="C106" s="7"/>
       <c r="D106" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F106" s="6">
         <v>2</v>
@@ -4465,10 +4314,10 @@
       </c>
       <c r="C107" s="7"/>
       <c r="D107" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F107" s="6">
         <v>2</v>
@@ -4489,10 +4338,10 @@
       </c>
       <c r="C108" s="7"/>
       <c r="D108" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F108" s="6">
         <v>2</v>
@@ -4513,10 +4362,10 @@
       </c>
       <c r="C109" s="7"/>
       <c r="D109" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F109" s="6">
         <v>2</v>
@@ -4537,10 +4386,10 @@
       </c>
       <c r="C110" s="7"/>
       <c r="D110" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F110" s="6">
         <v>2</v>
@@ -4561,10 +4410,10 @@
       </c>
       <c r="C111" s="7"/>
       <c r="D111" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F111" s="6">
         <v>2</v>
@@ -4585,10 +4434,10 @@
       </c>
       <c r="C112" s="7"/>
       <c r="D112" s="7" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F112" s="6">
         <v>2</v>
@@ -4609,10 +4458,10 @@
       </c>
       <c r="C113" s="7"/>
       <c r="D113" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F113" s="6">
         <v>2</v>
@@ -4633,10 +4482,10 @@
       </c>
       <c r="C114" s="7"/>
       <c r="D114" s="7" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F114" s="6">
         <v>2</v>
@@ -4657,10 +4506,10 @@
       </c>
       <c r="C115" s="7"/>
       <c r="D115" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F115" s="6">
         <v>2</v>
@@ -4681,10 +4530,10 @@
       </c>
       <c r="C116" s="7"/>
       <c r="D116" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F116" s="6">
         <v>2</v>
@@ -4705,10 +4554,10 @@
       </c>
       <c r="C117" s="7"/>
       <c r="D117" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F117" s="6">
         <v>2</v>
@@ -4729,10 +4578,10 @@
       </c>
       <c r="C118" s="7"/>
       <c r="D118" s="7" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F118" s="6">
         <v>2</v>
@@ -4753,10 +4602,10 @@
       </c>
       <c r="C119" s="7"/>
       <c r="D119" s="7" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F119" s="6">
         <v>2</v>
@@ -4777,10 +4626,10 @@
       </c>
       <c r="C120" s="7"/>
       <c r="D120" s="7" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F120" s="6">
         <v>2</v>
@@ -4801,10 +4650,10 @@
       </c>
       <c r="C121" s="7"/>
       <c r="D121" s="7" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F121" s="6">
         <v>2</v>
@@ -4825,10 +4674,10 @@
       </c>
       <c r="C122" s="7"/>
       <c r="D122" s="7" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F122" s="6">
         <v>2</v>
@@ -4849,10 +4698,10 @@
       </c>
       <c r="C123" s="7"/>
       <c r="D123" s="7" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F123" s="6">
         <v>2</v>
@@ -4873,10 +4722,10 @@
       </c>
       <c r="C124" s="7"/>
       <c r="D124" s="7" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F124" s="6">
         <v>2</v>
@@ -4897,10 +4746,10 @@
       </c>
       <c r="C125" s="7"/>
       <c r="D125" s="7" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F125" s="6">
         <v>2</v>
@@ -4921,10 +4770,10 @@
       </c>
       <c r="C126" s="7"/>
       <c r="D126" s="7" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F126" s="6">
         <v>2</v>
@@ -4945,10 +4794,10 @@
       </c>
       <c r="C127" s="7"/>
       <c r="D127" s="7" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F127" s="6">
         <v>2</v>
@@ -4969,10 +4818,10 @@
       </c>
       <c r="C128" s="7"/>
       <c r="D128" s="7" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F128" s="6">
         <v>2</v>
@@ -4993,10 +4842,10 @@
       </c>
       <c r="C129" s="7"/>
       <c r="D129" s="7" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F129" s="6">
         <v>2</v>
@@ -5017,10 +4866,10 @@
       </c>
       <c r="C130" s="7"/>
       <c r="D130" s="7" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F130" s="6">
         <v>2</v>
@@ -5041,10 +4890,10 @@
       </c>
       <c r="C131" s="7"/>
       <c r="D131" s="7" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F131" s="6">
         <v>2</v>
@@ -5065,10 +4914,10 @@
       </c>
       <c r="C132" s="7"/>
       <c r="D132" s="7" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F132" s="6">
         <v>2</v>
@@ -5089,10 +4938,10 @@
       </c>
       <c r="C133" s="7"/>
       <c r="D133" s="7" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F133" s="6">
         <v>2</v>
@@ -5113,10 +4962,10 @@
       </c>
       <c r="C134" s="7"/>
       <c r="D134" s="7" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F134" s="6">
         <v>2</v>
@@ -5137,10 +4986,10 @@
       </c>
       <c r="C135" s="7"/>
       <c r="D135" s="7" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F135" s="6">
         <v>2</v>
@@ -5161,10 +5010,10 @@
       </c>
       <c r="C136" s="7"/>
       <c r="D136" s="7" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F136" s="6">
         <v>2</v>
@@ -5185,10 +5034,10 @@
       </c>
       <c r="C137" s="7"/>
       <c r="D137" s="7" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F137" s="6">
         <v>2</v>
@@ -5209,10 +5058,10 @@
       </c>
       <c r="C138" s="7"/>
       <c r="D138" s="7" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F138" s="6">
         <v>2</v>
@@ -5233,10 +5082,10 @@
       </c>
       <c r="C139" s="7"/>
       <c r="D139" s="7" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F139" s="6">
         <v>2</v>
@@ -5257,10 +5106,10 @@
       </c>
       <c r="C140" s="7"/>
       <c r="D140" s="7" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F140" s="6">
         <v>2</v>
@@ -5281,10 +5130,10 @@
       </c>
       <c r="C141" s="7"/>
       <c r="D141" s="7" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F141" s="6">
         <v>2</v>
@@ -5305,10 +5154,10 @@
       </c>
       <c r="C142" s="7"/>
       <c r="D142" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F142" s="6">
         <v>2</v>
@@ -5329,10 +5178,10 @@
       </c>
       <c r="C143" s="7"/>
       <c r="D143" s="7" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F143" s="6">
         <v>2</v>
@@ -5353,10 +5202,10 @@
       </c>
       <c r="C144" s="7"/>
       <c r="D144" s="7" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F144" s="6">
         <v>2</v>
@@ -5377,10 +5226,10 @@
       </c>
       <c r="C145" s="7"/>
       <c r="D145" s="7" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F145" s="6">
         <v>2</v>
@@ -5401,10 +5250,10 @@
       </c>
       <c r="C146" s="7"/>
       <c r="D146" s="7" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F146" s="6">
         <v>2</v>
@@ -5425,10 +5274,10 @@
       </c>
       <c r="C147" s="7"/>
       <c r="D147" s="7" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F147" s="6">
         <v>2</v>
@@ -5449,10 +5298,10 @@
       </c>
       <c r="C148" s="7"/>
       <c r="D148" s="7" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F148" s="6">
         <v>2</v>
@@ -5473,10 +5322,10 @@
       </c>
       <c r="C149" s="7"/>
       <c r="D149" s="7" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F149" s="6">
         <v>2</v>
@@ -5497,10 +5346,10 @@
       </c>
       <c r="C150" s="7"/>
       <c r="D150" s="7" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F150" s="6">
         <v>2</v>
@@ -5521,10 +5370,10 @@
       </c>
       <c r="C151" s="7"/>
       <c r="D151" s="7" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F151" s="6">
         <v>2</v>
@@ -5545,10 +5394,10 @@
       </c>
       <c r="C152" s="7"/>
       <c r="D152" s="7" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F152" s="6">
         <v>2</v>
@@ -5569,10 +5418,10 @@
       </c>
       <c r="C153" s="7"/>
       <c r="D153" s="7" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F153" s="6">
         <v>2</v>
@@ -5593,10 +5442,10 @@
       </c>
       <c r="C154" s="7"/>
       <c r="D154" s="7" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F154" s="6">
         <v>2</v>
@@ -5617,10 +5466,10 @@
       </c>
       <c r="C155" s="7"/>
       <c r="D155" s="7" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F155" s="6">
         <v>2</v>
@@ -5641,10 +5490,10 @@
       </c>
       <c r="C156" s="7"/>
       <c r="D156" s="7" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F156" s="6">
         <v>2</v>
@@ -5665,10 +5514,10 @@
       </c>
       <c r="C157" s="7"/>
       <c r="D157" s="7" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F157" s="6">
         <v>2</v>
@@ -5689,10 +5538,10 @@
       </c>
       <c r="C158" s="7"/>
       <c r="D158" s="7" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F158" s="6">
         <v>2</v>
@@ -5713,10 +5562,10 @@
       </c>
       <c r="C159" s="7"/>
       <c r="D159" s="7" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F159" s="6">
         <v>2</v>
@@ -5737,10 +5586,10 @@
       </c>
       <c r="C160" s="7"/>
       <c r="D160" s="7" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F160" s="6">
         <v>2</v>
@@ -5761,10 +5610,10 @@
       </c>
       <c r="C161" s="7"/>
       <c r="D161" s="7" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F161" s="6">
         <v>2</v>
@@ -5785,10 +5634,10 @@
       </c>
       <c r="C162" s="7"/>
       <c r="D162" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F162" s="6">
         <v>2</v>
@@ -5809,10 +5658,10 @@
       </c>
       <c r="C163" s="7"/>
       <c r="D163" s="7" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F163" s="6">
         <v>2</v>
@@ -5833,10 +5682,10 @@
       </c>
       <c r="C164" s="7"/>
       <c r="D164" s="7" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F164" s="6">
         <v>2</v>
@@ -5857,10 +5706,10 @@
       </c>
       <c r="C165" s="7"/>
       <c r="D165" s="7" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F165" s="6">
         <v>2</v>
@@ -5881,10 +5730,10 @@
       </c>
       <c r="C166" s="7"/>
       <c r="D166" s="7" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F166" s="6">
         <v>2</v>
@@ -5905,10 +5754,10 @@
       </c>
       <c r="C167" s="7"/>
       <c r="D167" s="7" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F167" s="6">
         <v>2</v>
@@ -5929,10 +5778,10 @@
       </c>
       <c r="C168" s="7"/>
       <c r="D168" s="7" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F168" s="6">
         <v>2</v>
@@ -5953,10 +5802,10 @@
       </c>
       <c r="C169" s="7"/>
       <c r="D169" s="7" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F169" s="6">
         <v>2</v>
@@ -5977,10 +5826,10 @@
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F170" s="6">
         <v>2</v>
@@ -6001,10 +5850,10 @@
       </c>
       <c r="C171" s="7"/>
       <c r="D171" s="7" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F171" s="6">
         <v>2</v>
@@ -6025,10 +5874,10 @@
       </c>
       <c r="C172" s="7"/>
       <c r="D172" s="7" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F172" s="6">
         <v>2</v>
@@ -6049,10 +5898,10 @@
       </c>
       <c r="C173" s="7"/>
       <c r="D173" s="7" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F173" s="6">
         <v>2</v>
@@ -6073,10 +5922,10 @@
       </c>
       <c r="C174" s="7"/>
       <c r="D174" s="7" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E174" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F174" s="6">
         <v>2</v>
@@ -6097,10 +5946,10 @@
       </c>
       <c r="C175" s="7"/>
       <c r="D175" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F175" s="6">
         <v>2</v>
@@ -6121,10 +5970,10 @@
       </c>
       <c r="C176" s="7"/>
       <c r="D176" s="7" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F176" s="6">
         <v>2</v>
@@ -6145,10 +5994,10 @@
       </c>
       <c r="C177" s="7"/>
       <c r="D177" s="7" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F177" s="6">
         <v>2</v>
@@ -6169,10 +6018,10 @@
       </c>
       <c r="C178" s="7"/>
       <c r="D178" s="7" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F178" s="6">
         <v>2</v>
@@ -6193,10 +6042,10 @@
       </c>
       <c r="C179" s="7"/>
       <c r="D179" s="7" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F179" s="6">
         <v>2</v>
@@ -6217,10 +6066,10 @@
       </c>
       <c r="C180" s="7"/>
       <c r="D180" s="7" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F180" s="6">
         <v>2</v>
@@ -6241,10 +6090,10 @@
       </c>
       <c r="C181" s="7"/>
       <c r="D181" s="7" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F181" s="6">
         <v>2</v>
@@ -6265,10 +6114,10 @@
       </c>
       <c r="C182" s="7"/>
       <c r="D182" s="7" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F182" s="6">
         <v>2</v>
@@ -6289,10 +6138,10 @@
       </c>
       <c r="C183" s="7"/>
       <c r="D183" s="7" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F183" s="6">
         <v>2</v>
@@ -6313,10 +6162,10 @@
       </c>
       <c r="C184" s="7"/>
       <c r="D184" s="7" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F184" s="6">
         <v>2</v>
@@ -6337,10 +6186,10 @@
       </c>
       <c r="C185" s="7"/>
       <c r="D185" s="7" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F185" s="6">
         <v>2</v>
@@ -6361,10 +6210,10 @@
       </c>
       <c r="C186" s="7"/>
       <c r="D186" s="7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F186" s="6">
         <v>2</v>
@@ -6385,10 +6234,10 @@
       </c>
       <c r="C187" s="7"/>
       <c r="D187" s="7" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F187" s="6">
         <v>2</v>
@@ -6409,10 +6258,10 @@
       </c>
       <c r="C188" s="7"/>
       <c r="D188" s="7" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F188" s="6">
         <v>2</v>
@@ -6433,10 +6282,10 @@
       </c>
       <c r="C189" s="7"/>
       <c r="D189" s="7" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F189" s="6">
         <v>2</v>
@@ -6457,10 +6306,10 @@
       </c>
       <c r="C190" s="7"/>
       <c r="D190" s="7" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F190" s="6">
         <v>2</v>
@@ -6481,10 +6330,10 @@
       </c>
       <c r="C191" s="7"/>
       <c r="D191" s="7" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E191" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F191" s="6">
         <v>2</v>
@@ -6505,10 +6354,10 @@
       </c>
       <c r="C192" s="7"/>
       <c r="D192" s="7" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E192" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F192" s="6">
         <v>2</v>
@@ -6529,10 +6378,10 @@
       </c>
       <c r="C193" s="7"/>
       <c r="D193" s="7" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F193" s="6">
         <v>2</v>
@@ -6553,10 +6402,10 @@
       </c>
       <c r="C194" s="7"/>
       <c r="D194" s="7" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F194" s="6">
         <v>2</v>
@@ -6577,10 +6426,10 @@
       </c>
       <c r="C195" s="7"/>
       <c r="D195" s="7" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F195" s="6">
         <v>2</v>
@@ -6601,10 +6450,10 @@
       </c>
       <c r="C196" s="7"/>
       <c r="D196" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F196" s="6">
         <v>2</v>
@@ -6625,10 +6474,10 @@
       </c>
       <c r="C197" s="7"/>
       <c r="D197" s="7" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F197" s="6">
         <v>2</v>
@@ -6649,10 +6498,10 @@
       </c>
       <c r="C198" s="7"/>
       <c r="D198" s="7" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E198" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F198" s="6">
         <v>2</v>
@@ -6673,10 +6522,10 @@
       </c>
       <c r="C199" s="7"/>
       <c r="D199" s="7" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F199" s="6">
         <v>2</v>
@@ -6697,10 +6546,10 @@
       </c>
       <c r="C200" s="7"/>
       <c r="D200" s="7" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E200" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F200" s="6">
         <v>2</v>
@@ -6721,10 +6570,10 @@
       </c>
       <c r="C201" s="7"/>
       <c r="D201" s="7" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F201" s="6">
         <v>2</v>
@@ -6745,10 +6594,10 @@
       </c>
       <c r="C202" s="7"/>
       <c r="D202" s="7" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F202" s="6">
         <v>2</v>
@@ -6769,10 +6618,10 @@
       </c>
       <c r="C203" s="7"/>
       <c r="D203" s="7" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F203" s="6">
         <v>2</v>
@@ -6793,10 +6642,10 @@
       </c>
       <c r="C204" s="7"/>
       <c r="D204" s="7" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F204" s="6">
         <v>2</v>
@@ -6817,10 +6666,10 @@
       </c>
       <c r="C205" s="7"/>
       <c r="D205" s="7" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F205" s="6">
         <v>2</v>
@@ -6841,10 +6690,10 @@
       </c>
       <c r="C206" s="7"/>
       <c r="D206" s="7" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F206" s="6">
         <v>2</v>
@@ -6865,10 +6714,10 @@
       </c>
       <c r="C207" s="7"/>
       <c r="D207" s="7" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F207" s="6">
         <v>2</v>
@@ -6889,10 +6738,10 @@
       </c>
       <c r="C208" s="7"/>
       <c r="D208" s="7" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F208" s="6">
         <v>2</v>
@@ -6913,10 +6762,10 @@
       </c>
       <c r="C209" s="7"/>
       <c r="D209" s="7" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F209" s="6">
         <v>2</v>
@@ -6937,10 +6786,10 @@
       </c>
       <c r="C210" s="7"/>
       <c r="D210" s="7" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F210" s="6">
         <v>2</v>
@@ -6961,10 +6810,10 @@
       </c>
       <c r="C211" s="7"/>
       <c r="D211" s="7" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F211" s="6">
         <v>2</v>
@@ -6985,10 +6834,10 @@
       </c>
       <c r="C212" s="7"/>
       <c r="D212" s="7" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F212" s="6">
         <v>2</v>
@@ -7009,10 +6858,10 @@
       </c>
       <c r="C213" s="7"/>
       <c r="D213" s="7" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F213" s="6">
         <v>2</v>
@@ -7033,10 +6882,10 @@
       </c>
       <c r="C214" s="7"/>
       <c r="D214" s="7" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F214" s="6">
         <v>2</v>
@@ -7057,10 +6906,10 @@
       </c>
       <c r="C215" s="7"/>
       <c r="D215" s="7" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F215" s="6">
         <v>2</v>
@@ -7081,10 +6930,10 @@
       </c>
       <c r="C216" s="7"/>
       <c r="D216" s="7" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E216" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F216" s="6">
         <v>2</v>
@@ -7103,14 +6952,12 @@
       <c r="B217" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C217" s="7" t="s">
-        <v>351</v>
-      </c>
+      <c r="C217" s="7"/>
       <c r="D217" s="7" t="s">
-        <v>351</v>
+        <v>46</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F217" s="6">
         <v>1</v>
@@ -7129,14 +6976,12 @@
       <c r="B218" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C218" s="7" t="s">
-        <v>352</v>
-      </c>
+      <c r="C218" s="7"/>
       <c r="D218" s="7" t="s">
-        <v>352</v>
+        <v>47</v>
       </c>
       <c r="E218" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F218" s="6">
         <v>1</v>
@@ -7155,14 +7000,12 @@
       <c r="B219" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C219" s="7" t="s">
-        <v>353</v>
-      </c>
+      <c r="C219" s="7"/>
       <c r="D219" s="7" t="s">
-        <v>353</v>
+        <v>48</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F219" s="6">
         <v>1</v>
@@ -7181,14 +7024,12 @@
       <c r="B220" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C220" s="7" t="s">
-        <v>354</v>
-      </c>
+      <c r="C220" s="7"/>
       <c r="D220" s="7" t="s">
-        <v>354</v>
+        <v>49</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F220" s="6">
         <v>1</v>
@@ -7207,14 +7048,12 @@
       <c r="B221" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C221" s="7" t="s">
-        <v>355</v>
-      </c>
+      <c r="C221" s="7"/>
       <c r="D221" s="7" t="s">
-        <v>355</v>
+        <v>50</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F221" s="6">
         <v>1</v>
@@ -7233,14 +7072,12 @@
       <c r="B222" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C222" s="7" t="s">
-        <v>356</v>
-      </c>
+      <c r="C222" s="7"/>
       <c r="D222" s="7" t="s">
-        <v>356</v>
+        <v>51</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F222" s="6">
         <v>1</v>
@@ -7259,14 +7096,12 @@
       <c r="B223" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C223" s="7" t="s">
-        <v>357</v>
-      </c>
+      <c r="C223" s="7"/>
       <c r="D223" s="7" t="s">
-        <v>357</v>
+        <v>52</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F223" s="6">
         <v>1</v>
@@ -7285,14 +7120,12 @@
       <c r="B224" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C224" s="7" t="s">
-        <v>358</v>
-      </c>
+      <c r="C224" s="7"/>
       <c r="D224" s="7" t="s">
-        <v>358</v>
+        <v>53</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F224" s="6">
         <v>1</v>
@@ -7311,14 +7144,12 @@
       <c r="B225" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C225" s="7" t="s">
-        <v>359</v>
-      </c>
+      <c r="C225" s="7"/>
       <c r="D225" s="7" t="s">
-        <v>359</v>
+        <v>54</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F225" s="6">
         <v>1</v>
@@ -7337,14 +7168,12 @@
       <c r="B226" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C226" s="7" t="s">
-        <v>360</v>
-      </c>
+      <c r="C226" s="7"/>
       <c r="D226" s="7" t="s">
-        <v>360</v>
+        <v>55</v>
       </c>
       <c r="E226" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F226" s="6">
         <v>1</v>
@@ -7363,14 +7192,12 @@
       <c r="B227" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C227" s="7" t="s">
-        <v>361</v>
-      </c>
+      <c r="C227" s="7"/>
       <c r="D227" s="7" t="s">
-        <v>361</v>
+        <v>56</v>
       </c>
       <c r="E227" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F227" s="6">
         <v>1</v>
@@ -7389,14 +7216,12 @@
       <c r="B228" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C228" s="7" t="s">
-        <v>362</v>
-      </c>
+      <c r="C228" s="7"/>
       <c r="D228" s="7" t="s">
-        <v>362</v>
+        <v>57</v>
       </c>
       <c r="E228" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F228" s="6">
         <v>1</v>
@@ -7410,25 +7235,25 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>363</v>
+        <v>195</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>363</v>
+        <v>34</v>
       </c>
       <c r="E229" s="7" t="s">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="F229" s="6">
         <v>1</v>
       </c>
       <c r="G229" s="5">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H229" t="s">
         <v>23</v>
@@ -7442,19 +7267,19 @@
         <v>25</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D230" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E230" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F230" s="6">
         <v>1</v>
       </c>
       <c r="G230" s="5">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H230" t="s">
         <v>23</v>
@@ -7468,19 +7293,19 @@
         <v>25</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D231" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F231" s="6">
         <v>1</v>
       </c>
       <c r="G231" s="5">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H231" t="s">
         <v>23</v>
@@ -7494,19 +7319,19 @@
         <v>25</v>
       </c>
       <c r="C232" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D232" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E232" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F232" s="6">
         <v>1</v>
       </c>
       <c r="G232" s="5">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H232" t="s">
         <v>23</v>
@@ -7520,19 +7345,19 @@
         <v>25</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D233" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E233" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F233" s="6">
         <v>1</v>
       </c>
       <c r="G233" s="5">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H233" t="s">
         <v>23</v>
@@ -7546,19 +7371,19 @@
         <v>25</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D234" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F234" s="6">
         <v>1</v>
       </c>
       <c r="G234" s="5">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H234" t="s">
         <v>23</v>
@@ -7572,19 +7397,19 @@
         <v>25</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D235" s="7" t="s">
-        <v>39</v>
+        <v>197</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F235" s="6">
         <v>1</v>
       </c>
       <c r="G235" s="5">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H235" t="s">
         <v>23</v>
@@ -7598,19 +7423,19 @@
         <v>25</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D236" s="7" t="s">
-        <v>206</v>
+        <v>40</v>
       </c>
       <c r="E236" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F236" s="6">
         <v>1</v>
       </c>
       <c r="G236" s="5">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H236" t="s">
         <v>23</v>
@@ -7624,19 +7449,19 @@
         <v>25</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D237" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E237" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F237" s="6">
         <v>1</v>
       </c>
       <c r="G237" s="5">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H237" t="s">
         <v>23</v>
@@ -7650,19 +7475,19 @@
         <v>25</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D238" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E238" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F238" s="6">
         <v>1</v>
       </c>
       <c r="G238" s="5">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H238" t="s">
         <v>23</v>
@@ -7676,19 +7501,19 @@
         <v>25</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D239" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F239" s="6">
         <v>1</v>
       </c>
       <c r="G239" s="5">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H239" t="s">
         <v>23</v>
@@ -7702,19 +7527,19 @@
         <v>25</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D240" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F240" s="6">
         <v>1</v>
       </c>
       <c r="G240" s="5">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H240" t="s">
         <v>23</v>
@@ -7728,19 +7553,19 @@
         <v>25</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D241" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F241" s="6">
         <v>1</v>
       </c>
       <c r="G241" s="5">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H241" t="s">
         <v>23</v>
@@ -7754,19 +7579,19 @@
         <v>25</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D242" s="7" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="E242" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F242" s="6">
         <v>1</v>
       </c>
       <c r="G242" s="5">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H242" t="s">
         <v>23</v>
@@ -7780,19 +7605,19 @@
         <v>25</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D243" s="7" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F243" s="6">
         <v>1</v>
       </c>
       <c r="G243" s="5">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H243" t="s">
         <v>23</v>
@@ -7806,19 +7631,19 @@
         <v>25</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D244" s="7" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F244" s="6">
         <v>1</v>
       </c>
       <c r="G244" s="5">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H244" t="s">
         <v>23</v>
@@ -7832,19 +7657,19 @@
         <v>25</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D245" s="7" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E245" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F245" s="6">
         <v>1</v>
       </c>
       <c r="G245" s="5">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H245" t="s">
         <v>23</v>
@@ -7858,19 +7683,19 @@
         <v>25</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D246" s="7" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E246" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F246" s="6">
         <v>1</v>
       </c>
       <c r="G246" s="5">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H246" t="s">
         <v>23</v>
@@ -7884,19 +7709,19 @@
         <v>25</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D247" s="7" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F247" s="6">
         <v>1</v>
       </c>
       <c r="G247" s="5">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H247" t="s">
         <v>23</v>
@@ -7910,19 +7735,19 @@
         <v>25</v>
       </c>
       <c r="C248" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D248" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D248" s="7" t="s">
-        <v>212</v>
-      </c>
       <c r="E248" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F248" s="6">
         <v>1</v>
       </c>
       <c r="G248" s="5">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H248" t="s">
         <v>23</v>
@@ -7936,19 +7761,19 @@
         <v>25</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D249" s="7" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E249" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F249" s="6">
         <v>1</v>
       </c>
       <c r="G249" s="5">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H249" t="s">
         <v>23</v>
@@ -7962,19 +7787,19 @@
         <v>25</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D250" s="7" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="E250" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F250" s="6">
         <v>1</v>
       </c>
       <c r="G250" s="5">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H250" t="s">
         <v>23</v>
@@ -7988,19 +7813,19 @@
         <v>25</v>
       </c>
       <c r="C251" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D251" s="7" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E251" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F251" s="6">
         <v>1</v>
       </c>
       <c r="G251" s="5">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H251" t="s">
         <v>23</v>
@@ -8014,19 +7839,19 @@
         <v>25</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D252" s="7" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E252" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F252" s="6">
         <v>1</v>
       </c>
       <c r="G252" s="5">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H252" t="s">
         <v>23</v>
@@ -8040,19 +7865,19 @@
         <v>25</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D253" s="7" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E253" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F253" s="6">
         <v>1</v>
       </c>
       <c r="G253" s="5">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H253" t="s">
         <v>23</v>
@@ -8066,19 +7891,19 @@
         <v>25</v>
       </c>
       <c r="C254" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D254" s="7" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E254" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F254" s="6">
         <v>1</v>
       </c>
       <c r="G254" s="5">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H254" t="s">
         <v>23</v>
@@ -8092,19 +7917,19 @@
         <v>25</v>
       </c>
       <c r="C255" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D255" s="7" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F255" s="6">
         <v>1</v>
       </c>
       <c r="G255" s="5">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H255" t="s">
         <v>23</v>
@@ -8118,19 +7943,19 @@
         <v>25</v>
       </c>
       <c r="C256" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D256" s="7" t="s">
-        <v>221</v>
+        <v>315</v>
       </c>
       <c r="E256" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F256" s="6">
         <v>1</v>
       </c>
       <c r="G256" s="5">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H256" t="s">
         <v>23</v>
@@ -8144,19 +7969,19 @@
         <v>25</v>
       </c>
       <c r="C257" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D257" s="7" t="s">
-        <v>222</v>
+        <v>316</v>
       </c>
       <c r="E257" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F257" s="6">
         <v>1</v>
       </c>
       <c r="G257" s="5">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H257" t="s">
         <v>23</v>
@@ -8170,19 +7995,19 @@
         <v>25</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D258" s="7" t="s">
-        <v>223</v>
+        <v>317</v>
       </c>
       <c r="E258" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F258" s="6">
         <v>1</v>
       </c>
       <c r="G258" s="5">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H258" t="s">
         <v>23</v>
@@ -8196,19 +8021,19 @@
         <v>25</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D259" s="7" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="E259" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F259" s="6">
         <v>1</v>
       </c>
       <c r="G259" s="5">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H259" t="s">
         <v>23</v>
@@ -8222,19 +8047,19 @@
         <v>25</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D260" s="7" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="E260" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F260" s="6">
         <v>1</v>
       </c>
       <c r="G260" s="5">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H260" t="s">
         <v>23</v>
@@ -8248,19 +8073,19 @@
         <v>25</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D261" s="7" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="E261" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F261" s="6">
         <v>1</v>
       </c>
       <c r="G261" s="5">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H261" t="s">
         <v>23</v>
@@ -8277,16 +8102,16 @@
         <v>215</v>
       </c>
       <c r="D262" s="7" t="s">
-        <v>227</v>
+        <v>46</v>
       </c>
       <c r="E262" s="7" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="F262" s="6">
         <v>1</v>
       </c>
       <c r="G262" s="5">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H262" t="s">
         <v>23</v>
@@ -8300,19 +8125,19 @@
         <v>25</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D263" s="7" t="s">
-        <v>229</v>
+        <v>47</v>
       </c>
       <c r="E263" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F263" s="6">
         <v>1</v>
       </c>
       <c r="G263" s="5">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H263" t="s">
         <v>23</v>
@@ -8326,19 +8151,19 @@
         <v>25</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D264" s="7" t="s">
-        <v>231</v>
+        <v>48</v>
       </c>
       <c r="E264" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F264" s="6">
         <v>1</v>
       </c>
       <c r="G264" s="5">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H264" t="s">
         <v>23</v>
@@ -8352,19 +8177,19 @@
         <v>25</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D265" s="7" t="s">
-        <v>232</v>
+        <v>37</v>
       </c>
       <c r="E265" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F265" s="6">
         <v>1</v>
       </c>
       <c r="G265" s="5">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H265" t="s">
         <v>23</v>
@@ -8378,19 +8203,19 @@
         <v>25</v>
       </c>
       <c r="C266" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D266" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E266" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F266" s="6">
         <v>1</v>
       </c>
       <c r="G266" s="5">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H266" t="s">
         <v>23</v>
@@ -8404,19 +8229,19 @@
         <v>25</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D267" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E267" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F267" s="6">
         <v>1</v>
       </c>
       <c r="G267" s="5">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H267" t="s">
         <v>23</v>
@@ -8430,19 +8255,19 @@
         <v>25</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D268" s="7" t="s">
-        <v>233</v>
+        <v>40</v>
       </c>
       <c r="E268" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F268" s="6">
         <v>1</v>
       </c>
       <c r="G268" s="5">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H268" t="s">
         <v>23</v>
@@ -8456,19 +8281,19 @@
         <v>25</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D269" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E269" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F269" s="6">
         <v>1</v>
       </c>
       <c r="G269" s="5">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H269" t="s">
         <v>23</v>
@@ -8482,19 +8307,19 @@
         <v>25</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D270" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E270" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F270" s="6">
         <v>1</v>
       </c>
       <c r="G270" s="5">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H270" t="s">
         <v>23</v>
@@ -8508,19 +8333,19 @@
         <v>25</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D271" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E271" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F271" s="6">
         <v>1</v>
       </c>
       <c r="G271" s="5">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H271" t="s">
         <v>23</v>
@@ -8534,19 +8359,19 @@
         <v>25</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D272" s="7" t="s">
-        <v>43</v>
+        <v>217</v>
       </c>
       <c r="E272" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F272" s="6">
         <v>1</v>
       </c>
       <c r="G272" s="5">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H272" t="s">
         <v>23</v>
@@ -8560,19 +8385,19 @@
         <v>25</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D273" s="7" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E273" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F273" s="6">
         <v>1</v>
       </c>
       <c r="G273" s="5">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H273" t="s">
         <v>23</v>
@@ -8586,19 +8411,19 @@
         <v>25</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D274" s="7" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="E274" s="7" t="s">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="F274" s="6">
         <v>1</v>
       </c>
       <c r="G274" s="5">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H274" t="s">
         <v>23</v>
@@ -8612,19 +8437,19 @@
         <v>25</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D275" s="7" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="E275" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F275" s="6">
         <v>1</v>
       </c>
       <c r="G275" s="5">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H275" t="s">
         <v>23</v>
@@ -8638,19 +8463,19 @@
         <v>25</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D276" s="7" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="E276" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F276" s="6">
         <v>1</v>
       </c>
       <c r="G276" s="5">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H276" t="s">
         <v>23</v>
@@ -8664,19 +8489,19 @@
         <v>25</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D277" s="7" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="E277" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F277" s="6">
         <v>1</v>
       </c>
       <c r="G277" s="5">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H277" t="s">
         <v>23</v>
@@ -8690,19 +8515,19 @@
         <v>25</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D278" s="7" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="E278" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F278" s="6">
         <v>1</v>
       </c>
       <c r="G278" s="5">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H278" t="s">
         <v>23</v>
@@ -8716,19 +8541,19 @@
         <v>25</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D279" s="7" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E279" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F279" s="6">
         <v>1</v>
       </c>
       <c r="G279" s="5">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H279" t="s">
         <v>23</v>
@@ -8742,19 +8567,19 @@
         <v>25</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D280" s="7" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E280" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F280" s="6">
         <v>1</v>
       </c>
       <c r="G280" s="5">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H280" t="s">
         <v>23</v>
@@ -8768,19 +8593,19 @@
         <v>25</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D281" s="7" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="E281" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F281" s="6">
         <v>1</v>
       </c>
       <c r="G281" s="5">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H281" t="s">
         <v>23</v>
@@ -8794,19 +8619,19 @@
         <v>25</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D282" s="7" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E282" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F282" s="6">
         <v>1</v>
       </c>
       <c r="G282" s="5">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H282" t="s">
         <v>23</v>
@@ -8820,19 +8645,19 @@
         <v>25</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="E283" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F283" s="6">
         <v>1</v>
       </c>
       <c r="G283" s="5">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H283" t="s">
         <v>23</v>
@@ -8846,19 +8671,19 @@
         <v>25</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E284" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F284" s="6">
         <v>1</v>
       </c>
       <c r="G284" s="5">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H284" t="s">
         <v>23</v>
@@ -8872,19 +8697,19 @@
         <v>25</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D285" s="7" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="E285" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F285" s="6">
         <v>1</v>
       </c>
       <c r="G285" s="5">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H285" t="s">
         <v>23</v>
@@ -8898,19 +8723,19 @@
         <v>25</v>
       </c>
       <c r="C286" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D286" s="7" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F286" s="6">
         <v>1</v>
       </c>
       <c r="G286" s="5">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H286" t="s">
         <v>23</v>
@@ -8924,19 +8749,19 @@
         <v>25</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D287" s="7" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F287" s="6">
         <v>1</v>
       </c>
       <c r="G287" s="5">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H287" t="s">
         <v>23</v>
@@ -8950,19 +8775,19 @@
         <v>25</v>
       </c>
       <c r="C288" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D288" s="7" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="E288" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F288" s="6">
         <v>1</v>
       </c>
       <c r="G288" s="5">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H288" t="s">
         <v>23</v>
@@ -8976,19 +8801,19 @@
         <v>25</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D289" s="7" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F289" s="6">
         <v>1</v>
       </c>
       <c r="G289" s="5">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H289" t="s">
         <v>23</v>
@@ -9002,19 +8827,19 @@
         <v>25</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D290" s="7" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F290" s="6">
         <v>1</v>
       </c>
       <c r="G290" s="5">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H290" t="s">
         <v>23</v>
@@ -9028,19 +8853,19 @@
         <v>25</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D291" s="7" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="E291" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F291" s="6">
         <v>1</v>
       </c>
       <c r="G291" s="5">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H291" t="s">
         <v>23</v>
@@ -9054,19 +8879,19 @@
         <v>25</v>
       </c>
       <c r="C292" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D292" s="7" t="s">
-        <v>254</v>
+        <v>287</v>
       </c>
       <c r="E292" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F292" s="6">
         <v>1</v>
       </c>
       <c r="G292" s="5">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H292" t="s">
         <v>23</v>
@@ -9080,19 +8905,19 @@
         <v>25</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D293" s="7" t="s">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="E293" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F293" s="6">
         <v>1</v>
       </c>
       <c r="G293" s="5">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H293" t="s">
         <v>23</v>
@@ -9106,19 +8931,19 @@
         <v>25</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D294" s="7" t="s">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="E294" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F294" s="6">
         <v>1</v>
       </c>
       <c r="G294" s="5">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H294" t="s">
         <v>23</v>
@@ -9132,19 +8957,19 @@
         <v>25</v>
       </c>
       <c r="C295" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D295" s="7" t="s">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="E295" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F295" s="6">
         <v>1</v>
       </c>
       <c r="G295" s="5">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H295" t="s">
         <v>23</v>
@@ -9158,19 +8983,19 @@
         <v>25</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D296" s="7" t="s">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="E296" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F296" s="6">
         <v>1</v>
       </c>
       <c r="G296" s="5">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H296" t="s">
         <v>23</v>
@@ -9184,19 +9009,19 @@
         <v>25</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D297" s="7" t="s">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="E297" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F297" s="6">
         <v>1</v>
       </c>
       <c r="G297" s="5">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H297" t="s">
         <v>23</v>
@@ -9210,19 +9035,19 @@
         <v>25</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D298" s="7" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F298" s="6">
         <v>1</v>
       </c>
       <c r="G298" s="5">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H298" t="s">
         <v>23</v>
@@ -9236,19 +9061,19 @@
         <v>25</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D299" s="7" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F299" s="6">
         <v>1</v>
       </c>
       <c r="G299" s="5">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H299" t="s">
         <v>23</v>
@@ -9262,19 +9087,19 @@
         <v>25</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D300" s="7" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="E300" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F300" s="6">
         <v>1</v>
       </c>
       <c r="G300" s="5">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H300" t="s">
         <v>23</v>
@@ -9288,19 +9113,19 @@
         <v>25</v>
       </c>
       <c r="C301" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D301" s="7" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="E301" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F301" s="6">
         <v>1</v>
       </c>
       <c r="G301" s="5">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H301" t="s">
         <v>23</v>
@@ -9314,19 +9139,19 @@
         <v>25</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D302" s="7" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="E302" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F302" s="6">
         <v>1</v>
       </c>
       <c r="G302" s="5">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H302" t="s">
         <v>23</v>
@@ -9340,19 +9165,19 @@
         <v>25</v>
       </c>
       <c r="C303" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D303" s="7" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="E303" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F303" s="6">
         <v>1</v>
       </c>
       <c r="G303" s="5">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H303" t="s">
         <v>23</v>
@@ -9366,19 +9191,19 @@
         <v>25</v>
       </c>
       <c r="C304" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D304" s="7" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="E304" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F304" s="6">
         <v>1</v>
       </c>
       <c r="G304" s="5">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H304" t="s">
         <v>23</v>
@@ -9392,19 +9217,19 @@
         <v>25</v>
       </c>
       <c r="C305" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D305" s="7" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="E305" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F305" s="6">
         <v>1</v>
       </c>
       <c r="G305" s="5">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H305" t="s">
         <v>23</v>
@@ -9418,19 +9243,19 @@
         <v>25</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D306" s="7" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="E306" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F306" s="6">
         <v>1</v>
       </c>
       <c r="G306" s="5">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H306" t="s">
         <v>23</v>
@@ -9444,19 +9269,19 @@
         <v>25</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D307" s="7" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="E307" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F307" s="6">
         <v>1</v>
       </c>
       <c r="G307" s="5">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H307" t="s">
         <v>23</v>
@@ -9470,19 +9295,19 @@
         <v>25</v>
       </c>
       <c r="C308" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D308" s="7" t="s">
-        <v>271</v>
+        <v>234</v>
       </c>
       <c r="E308" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F308" s="6">
         <v>1</v>
       </c>
       <c r="G308" s="5">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H308" t="s">
         <v>23</v>
@@ -9496,19 +9321,19 @@
         <v>25</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D309" s="7" t="s">
-        <v>272</v>
+        <v>235</v>
       </c>
       <c r="E309" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F309" s="6">
         <v>1</v>
       </c>
       <c r="G309" s="5">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H309" t="s">
         <v>23</v>
@@ -9522,19 +9347,19 @@
         <v>25</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D310" s="7" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="E310" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F310" s="6">
         <v>1</v>
       </c>
       <c r="G310" s="5">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H310" t="s">
         <v>23</v>
@@ -9548,19 +9373,19 @@
         <v>25</v>
       </c>
       <c r="C311" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D311" s="7" t="s">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="E311" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F311" s="6">
         <v>1</v>
       </c>
       <c r="G311" s="5">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H311" t="s">
         <v>23</v>
@@ -9574,19 +9399,19 @@
         <v>25</v>
       </c>
       <c r="C312" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D312" s="7" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="E312" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F312" s="6">
         <v>1</v>
       </c>
       <c r="G312" s="5">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H312" t="s">
         <v>23</v>
@@ -9600,19 +9425,19 @@
         <v>25</v>
       </c>
       <c r="C313" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D313" s="7" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="E313" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F313" s="6">
         <v>1</v>
       </c>
       <c r="G313" s="5">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H313" t="s">
         <v>23</v>
@@ -9626,19 +9451,19 @@
         <v>25</v>
       </c>
       <c r="C314" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D314" s="7" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="E314" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F314" s="6">
         <v>1</v>
       </c>
       <c r="G314" s="5">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H314" t="s">
         <v>23</v>
@@ -9652,19 +9477,19 @@
         <v>25</v>
       </c>
       <c r="C315" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D315" s="7" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="E315" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F315" s="6">
         <v>1</v>
       </c>
       <c r="G315" s="5">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H315" t="s">
         <v>23</v>
@@ -9678,19 +9503,19 @@
         <v>25</v>
       </c>
       <c r="C316" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D316" s="7" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F316" s="6">
         <v>1</v>
       </c>
       <c r="G316" s="5">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H316" t="s">
         <v>23</v>
@@ -9704,19 +9529,19 @@
         <v>25</v>
       </c>
       <c r="C317" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D317" s="7" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="E317" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F317" s="6">
         <v>1</v>
       </c>
       <c r="G317" s="5">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H317" t="s">
         <v>23</v>
@@ -9730,19 +9555,19 @@
         <v>25</v>
       </c>
       <c r="C318" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D318" s="7" t="s">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="E318" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F318" s="6">
         <v>1</v>
       </c>
       <c r="G318" s="5">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H318" t="s">
         <v>23</v>
@@ -9756,19 +9581,19 @@
         <v>25</v>
       </c>
       <c r="C319" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D319" s="7" t="s">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F319" s="6">
         <v>1</v>
       </c>
       <c r="G319" s="5">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H319" t="s">
         <v>23</v>
@@ -9782,19 +9607,19 @@
         <v>25</v>
       </c>
       <c r="C320" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D320" s="7" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="E320" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F320" s="6">
         <v>1</v>
       </c>
       <c r="G320" s="5">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H320" t="s">
         <v>23</v>
@@ -9808,19 +9633,19 @@
         <v>25</v>
       </c>
       <c r="C321" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D321" s="7" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="E321" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F321" s="6">
         <v>1</v>
       </c>
       <c r="G321" s="5">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H321" t="s">
         <v>23</v>
@@ -9834,19 +9659,19 @@
         <v>25</v>
       </c>
       <c r="C322" s="7" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="D322" s="7" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="E322" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F322" s="6">
         <v>1</v>
       </c>
       <c r="G322" s="5">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H322" t="s">
         <v>23</v>
@@ -9860,19 +9685,19 @@
         <v>25</v>
       </c>
       <c r="C323" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D323" s="7" t="s">
-        <v>287</v>
+        <v>239</v>
       </c>
       <c r="E323" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F323" s="6">
         <v>1</v>
       </c>
       <c r="G323" s="5">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H323" t="s">
         <v>23</v>
@@ -9886,19 +9711,19 @@
         <v>25</v>
       </c>
       <c r="C324" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D324" s="7" t="s">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="E324" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F324" s="6">
         <v>1</v>
       </c>
       <c r="G324" s="5">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H324" t="s">
         <v>23</v>
@@ -9912,19 +9737,19 @@
         <v>25</v>
       </c>
       <c r="C325" s="7" t="s">
-        <v>286</v>
+        <v>206</v>
       </c>
       <c r="D325" s="7" t="s">
-        <v>289</v>
+        <v>247</v>
       </c>
       <c r="E325" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F325" s="6">
         <v>1</v>
       </c>
       <c r="G325" s="5">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H325" t="s">
         <v>23</v>
@@ -9938,19 +9763,19 @@
         <v>25</v>
       </c>
       <c r="C326" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D326" s="7" t="s">
-        <v>320</v>
+        <v>248</v>
       </c>
       <c r="E326" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F326" s="6">
         <v>1</v>
       </c>
       <c r="G326" s="5">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H326" t="s">
         <v>23</v>
@@ -9964,19 +9789,19 @@
         <v>25</v>
       </c>
       <c r="C327" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D327" s="7" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F327" s="6">
         <v>1</v>
       </c>
       <c r="G327" s="5">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H327" t="s">
         <v>23</v>
@@ -9990,19 +9815,19 @@
         <v>25</v>
       </c>
       <c r="C328" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D328" s="7" t="s">
-        <v>322</v>
+        <v>250</v>
       </c>
       <c r="E328" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F328" s="6">
         <v>1</v>
       </c>
       <c r="G328" s="5">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H328" t="s">
         <v>23</v>
@@ -10016,19 +9841,19 @@
         <v>25</v>
       </c>
       <c r="C329" s="7" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D329" s="7" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F329" s="6">
         <v>1</v>
       </c>
       <c r="G329" s="5">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H329" t="s">
         <v>23</v>
@@ -10042,19 +9867,19 @@
         <v>25</v>
       </c>
       <c r="C330" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D330" s="7" t="s">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="E330" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F330" s="6">
         <v>1</v>
       </c>
       <c r="G330" s="5">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H330" t="s">
         <v>23</v>
@@ -10068,19 +9893,19 @@
         <v>25</v>
       </c>
       <c r="C331" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D331" s="7" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="E331" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F331" s="6">
         <v>1</v>
       </c>
       <c r="G331" s="5">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H331" t="s">
         <v>23</v>
@@ -10094,19 +9919,19 @@
         <v>25</v>
       </c>
       <c r="C332" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D332" s="7" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="E332" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F332" s="6">
         <v>1</v>
       </c>
       <c r="G332" s="5">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H332" t="s">
         <v>23</v>
@@ -10120,19 +9945,19 @@
         <v>25</v>
       </c>
       <c r="C333" s="7" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="D333" s="7" t="s">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="E333" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F333" s="6">
         <v>1</v>
       </c>
       <c r="G333" s="5">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H333" t="s">
         <v>23</v>
@@ -10146,19 +9971,19 @@
         <v>25</v>
       </c>
       <c r="C334" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D334" s="7" t="s">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="E334" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F334" s="6">
         <v>1</v>
       </c>
       <c r="G334" s="5">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H334" t="s">
         <v>23</v>
@@ -10172,19 +9997,19 @@
         <v>25</v>
       </c>
       <c r="C335" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D335" s="7" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="E335" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F335" s="6">
         <v>1</v>
       </c>
       <c r="G335" s="5">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H335" t="s">
         <v>23</v>
@@ -10198,19 +10023,19 @@
         <v>25</v>
       </c>
       <c r="C336" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D336" s="7" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="E336" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F336" s="6">
         <v>1</v>
       </c>
       <c r="G336" s="5">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H336" t="s">
         <v>23</v>
@@ -10224,19 +10049,19 @@
         <v>25</v>
       </c>
       <c r="C337" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D337" s="7" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E337" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F337" s="6">
         <v>1</v>
       </c>
       <c r="G337" s="5">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H337" t="s">
         <v>23</v>
@@ -10250,19 +10075,19 @@
         <v>25</v>
       </c>
       <c r="C338" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D338" s="7" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="E338" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F338" s="6">
         <v>1</v>
       </c>
       <c r="G338" s="5">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H338" t="s">
         <v>23</v>
@@ -10276,19 +10101,19 @@
         <v>25</v>
       </c>
       <c r="C339" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D339" s="7" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="E339" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F339" s="6">
         <v>1</v>
       </c>
       <c r="G339" s="5">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H339" t="s">
         <v>23</v>
@@ -10302,19 +10127,19 @@
         <v>25</v>
       </c>
       <c r="C340" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D340" s="7" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="E340" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F340" s="6">
         <v>1</v>
       </c>
       <c r="G340" s="5">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H340" t="s">
         <v>23</v>
@@ -10328,19 +10153,19 @@
         <v>25</v>
       </c>
       <c r="C341" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D341" s="7" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="E341" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F341" s="6">
         <v>1</v>
       </c>
       <c r="G341" s="5">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H341" t="s">
         <v>23</v>
@@ -10354,19 +10179,19 @@
         <v>25</v>
       </c>
       <c r="C342" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D342" s="7" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="E342" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F342" s="6">
         <v>1</v>
       </c>
       <c r="G342" s="5">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H342" t="s">
         <v>23</v>
@@ -10380,19 +10205,19 @@
         <v>25</v>
       </c>
       <c r="C343" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D343" s="7" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="E343" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F343" s="6">
         <v>1</v>
       </c>
       <c r="G343" s="5">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H343" t="s">
         <v>23</v>
@@ -10406,19 +10231,19 @@
         <v>25</v>
       </c>
       <c r="C344" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D344" s="7" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="E344" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F344" s="6">
         <v>1</v>
       </c>
       <c r="G344" s="5">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H344" t="s">
         <v>23</v>
@@ -10432,19 +10257,19 @@
         <v>25</v>
       </c>
       <c r="C345" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D345" s="7" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="E345" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F345" s="6">
         <v>1</v>
       </c>
       <c r="G345" s="5">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H345" t="s">
         <v>23</v>
@@ -10458,19 +10283,19 @@
         <v>25</v>
       </c>
       <c r="C346" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D346" s="7" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="E346" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F346" s="6">
         <v>1</v>
       </c>
       <c r="G346" s="5">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H346" t="s">
         <v>23</v>
@@ -10484,19 +10309,19 @@
         <v>25</v>
       </c>
       <c r="C347" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D347" s="7" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="E347" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F347" s="6">
         <v>1</v>
       </c>
       <c r="G347" s="5">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H347" t="s">
         <v>23</v>
@@ -10510,19 +10335,19 @@
         <v>25</v>
       </c>
       <c r="C348" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D348" s="7" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="E348" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F348" s="6">
         <v>1</v>
       </c>
       <c r="G348" s="5">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H348" t="s">
         <v>23</v>
@@ -10536,19 +10361,19 @@
         <v>25</v>
       </c>
       <c r="C349" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D349" s="7" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="E349" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F349" s="6">
         <v>1</v>
       </c>
       <c r="G349" s="5">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H349" t="s">
         <v>23</v>
@@ -10562,19 +10387,19 @@
         <v>25</v>
       </c>
       <c r="C350" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D350" s="7" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="E350" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F350" s="6">
         <v>1</v>
       </c>
       <c r="G350" s="5">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H350" t="s">
         <v>23</v>
@@ -10588,19 +10413,19 @@
         <v>25</v>
       </c>
       <c r="C351" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D351" s="7" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="E351" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F351" s="6">
         <v>1</v>
       </c>
       <c r="G351" s="5">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H351" t="s">
         <v>23</v>
@@ -10614,19 +10439,19 @@
         <v>25</v>
       </c>
       <c r="C352" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D352" s="7" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="E352" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F352" s="6">
         <v>1</v>
       </c>
       <c r="G352" s="5">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H352" t="s">
         <v>23</v>
@@ -10640,19 +10465,19 @@
         <v>25</v>
       </c>
       <c r="C353" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D353" s="7" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="E353" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F353" s="6">
         <v>1</v>
       </c>
       <c r="G353" s="5">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H353" t="s">
         <v>23</v>
@@ -10666,19 +10491,19 @@
         <v>25</v>
       </c>
       <c r="C354" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D354" s="7" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="E354" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F354" s="6">
         <v>1</v>
       </c>
       <c r="G354" s="5">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H354" t="s">
         <v>23</v>
@@ -10692,62 +10517,36 @@
         <v>25</v>
       </c>
       <c r="C355" s="7" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="D355" s="7" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="E355" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F355" s="6">
         <v>1</v>
       </c>
       <c r="G355" s="5">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H355" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A356" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B356" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C356" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="D356" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="E356" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="F356" s="6">
-        <v>1</v>
-      </c>
-      <c r="G356" s="5">
-        <v>355</v>
-      </c>
-      <c r="H356" t="s">
-        <v>23</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H356" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H356">
-    <sortCondition ref="A2:A356"/>
-    <sortCondition ref="B2:B356"/>
+  <autoFilter ref="A1:H355" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H355">
+    <sortCondition ref="A2:A355"/>
+    <sortCondition ref="B2:B355"/>
   </sortState>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="H2:H356" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" sqref="D342 E329:E341 C342:C355 D2:D71 D86:D328" xr:uid="{00000000-0002-0000-0200-000000000000}">
+      <formula1>"habitacion,cubiculo,sillon,cama,camilla,area"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="H2:H355" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"SI,NO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="D2:D329 E330:E342 C343:C356 D343" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"habitacion,cubiculo,sillon,cama,camilla,area"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
